--- a/ig/DM-JANVIER-2025/ASS-A14-FamilleActivite-ActiviteOperationnelle.xlsx
+++ b/ig/DM-JANVIER-2025/ASS-A14-FamilleActivite-ActiviteOperationnelle.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="126">
   <si>
     <t>Property</t>
   </si>
@@ -93,7 +93,7 @@
     <t>Target</t>
   </si>
   <si>
-    <t>https://mos.esante.gouv.fr/NOS/TRE_R265-PrestationPilotageSerafin/FHIR/TRE-R265-PrestationPilotageSerafin</t>
+    <t>https://smt.esante.gouv.fr/terminologie-SERAFINPH</t>
   </si>
   <si>
     <t/>
@@ -102,7 +102,7 @@
     <t>https://mos.esante.gouv.fr/NOS/TRE_R211-ActiviteOperationnelle/FHIR/TRE-R211-ActiviteOperationnelle</t>
   </si>
   <si>
-    <t>004</t>
+    <t>2.1.1.1</t>
   </si>
   <si>
     <t>equivalent</t>
@@ -132,7 +132,7 @@
     <t>493</t>
   </si>
   <si>
-    <t>005</t>
+    <t>2.1.1.2</t>
   </si>
   <si>
     <t>287</t>
@@ -144,7 +144,7 @@
     <t>407</t>
   </si>
   <si>
-    <t>006</t>
+    <t>2.1.1.3</t>
   </si>
   <si>
     <t>289</t>
@@ -156,7 +156,7 @@
     <t>397</t>
   </si>
   <si>
-    <t>009</t>
+    <t>2.1.2.1</t>
   </si>
   <si>
     <t>290</t>
@@ -168,7 +168,7 @@
     <t>292</t>
   </si>
   <si>
-    <t>011</t>
+    <t>2.2.1.1</t>
   </si>
   <si>
     <t>293</t>
@@ -177,7 +177,7 @@
     <t>394</t>
   </si>
   <si>
-    <t>012</t>
+    <t>2.2.1.2</t>
   </si>
   <si>
     <t>294</t>
@@ -186,7 +186,7 @@
     <t>295</t>
   </si>
   <si>
-    <t>013</t>
+    <t>2.2.1.3</t>
   </si>
   <si>
     <t>296</t>
@@ -207,16 +207,19 @@
     <t>298</t>
   </si>
   <si>
+    <t>2.3.2.1</t>
+  </si>
+  <si>
     <t>401</t>
   </si>
   <si>
-    <t>020</t>
+    <t>2.3.2.2</t>
   </si>
   <si>
     <t>299</t>
   </si>
   <si>
-    <t>022</t>
+    <t>2.3.3.1</t>
   </si>
   <si>
     <t>300</t>
@@ -225,13 +228,13 @@
     <t>301</t>
   </si>
   <si>
-    <t>023</t>
+    <t>2.3.3.2</t>
   </si>
   <si>
     <t>302</t>
   </si>
   <si>
-    <t>024</t>
+    <t>2.3.3.3</t>
   </si>
   <si>
     <t>303</t>
@@ -243,7 +246,7 @@
     <t>305</t>
   </si>
   <si>
-    <t>025</t>
+    <t>2.3.3.4</t>
   </si>
   <si>
     <t>306</t>
@@ -252,7 +255,7 @@
     <t>307</t>
   </si>
   <si>
-    <t>026</t>
+    <t>2.3.3.5</t>
   </si>
   <si>
     <t>308</t>
@@ -264,7 +267,7 @@
     <t>342</t>
   </si>
   <si>
-    <t>027</t>
+    <t>2.3.3.6</t>
   </si>
   <si>
     <t>310</t>
@@ -273,7 +276,7 @@
     <t>311</t>
   </si>
   <si>
-    <t>029</t>
+    <t>2.3.4.1</t>
   </si>
   <si>
     <t>312</t>
@@ -285,6 +288,9 @@
     <t>313</t>
   </si>
   <si>
+    <t>2.3.4.2</t>
+  </si>
+  <si>
     <t>314</t>
   </si>
   <si>
@@ -297,6 +303,9 @@
     <t>316</t>
   </si>
   <si>
+    <t>2.3.4.3</t>
+  </si>
+  <si>
     <t>324</t>
   </si>
   <si>
@@ -309,13 +318,13 @@
     <t>404</t>
   </si>
   <si>
-    <t>034</t>
+    <t>2.3.5.1</t>
   </si>
   <si>
     <t>317</t>
   </si>
   <si>
-    <t>035</t>
+    <t>2.3.5.2</t>
   </si>
   <si>
     <t>318</t>
@@ -330,7 +339,7 @@
     <t>320</t>
   </si>
   <si>
-    <t>037</t>
+    <t>2.4</t>
   </si>
   <si>
     <t>335</t>
@@ -348,7 +357,7 @@
     <t>475</t>
   </si>
   <si>
-    <t>053</t>
+    <t>3.1.5</t>
   </si>
   <si>
     <t>321</t>
@@ -360,13 +369,13 @@
     <t>408</t>
   </si>
   <si>
-    <t>065</t>
+    <t>3.2.2.1</t>
   </si>
   <si>
     <t>322</t>
   </si>
   <si>
-    <t>067</t>
+    <t>3.2.3.1</t>
   </si>
   <si>
     <t>323</t>
@@ -978,534 +987,534 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" t="s" s="2">
         <v>30</v>
       </c>
       <c r="D27" t="s" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E27" s="2"/>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" t="s" s="2">
         <v>30</v>
       </c>
       <c r="D28" t="s" s="2">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E28" s="2"/>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" t="s" s="2">
         <v>30</v>
       </c>
       <c r="D29" t="s" s="2">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E29" s="2"/>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" t="s" s="2">
         <v>30</v>
       </c>
       <c r="D30" t="s" s="2">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="E30" s="2"/>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" t="s" s="2">
         <v>30</v>
       </c>
       <c r="D31" t="s" s="2">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E31" s="2"/>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" t="s" s="2">
         <v>30</v>
       </c>
       <c r="D32" t="s" s="2">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E32" s="2"/>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" t="s" s="2">
         <v>30</v>
       </c>
       <c r="D33" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E33" s="2"/>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" t="s" s="2">
         <v>30</v>
       </c>
       <c r="D34" t="s" s="2">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E34" s="2"/>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" t="s" s="2">
         <v>30</v>
       </c>
       <c r="D35" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E35" s="2"/>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B36" s="2"/>
       <c r="C36" t="s" s="2">
         <v>30</v>
       </c>
       <c r="D36" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E36" s="2"/>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" t="s" s="2">
         <v>30</v>
       </c>
       <c r="D37" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E37" s="2"/>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B38" s="2"/>
       <c r="C38" t="s" s="2">
         <v>30</v>
       </c>
       <c r="D38" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E38" s="2"/>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B39" s="2"/>
       <c r="C39" t="s" s="2">
         <v>30</v>
       </c>
       <c r="D39" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E39" s="2"/>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B40" s="2"/>
       <c r="C40" t="s" s="2">
         <v>30</v>
       </c>
       <c r="D40" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E40" s="2"/>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B41" s="2"/>
       <c r="C41" t="s" s="2">
         <v>30</v>
       </c>
       <c r="D41" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E41" s="2"/>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B42" s="2"/>
       <c r="C42" t="s" s="2">
         <v>30</v>
       </c>
       <c r="D42" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E42" s="2"/>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B43" s="2"/>
       <c r="C43" t="s" s="2">
         <v>30</v>
       </c>
       <c r="D43" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E43" s="2"/>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B44" s="2"/>
       <c r="C44" t="s" s="2">
         <v>30</v>
       </c>
       <c r="D44" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E44" s="2"/>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B45" s="2"/>
       <c r="C45" t="s" s="2">
         <v>30</v>
       </c>
       <c r="D45" t="s" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E45" s="2"/>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B46" s="2"/>
       <c r="C46" t="s" s="2">
         <v>30</v>
       </c>
       <c r="D46" t="s" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E46" s="2"/>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B47" s="2"/>
       <c r="C47" t="s" s="2">
         <v>30</v>
       </c>
       <c r="D47" t="s" s="2">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E47" s="2"/>
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B48" s="2"/>
       <c r="C48" t="s" s="2">
         <v>30</v>
       </c>
       <c r="D48" t="s" s="2">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="E48" s="2"/>
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B49" s="2"/>
       <c r="C49" t="s" s="2">
         <v>30</v>
       </c>
       <c r="D49" t="s" s="2">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="E49" s="2"/>
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B50" s="2"/>
       <c r="C50" t="s" s="2">
         <v>30</v>
       </c>
       <c r="D50" t="s" s="2">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="E50" s="2"/>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B51" s="2"/>
       <c r="C51" t="s" s="2">
         <v>30</v>
       </c>
       <c r="D51" t="s" s="2">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="E51" s="2"/>
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B52" s="2"/>
       <c r="C52" t="s" s="2">
         <v>30</v>
       </c>
       <c r="D52" t="s" s="2">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="E52" s="2"/>
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B53" s="2"/>
       <c r="C53" t="s" s="2">
         <v>30</v>
       </c>
       <c r="D53" t="s" s="2">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E53" s="2"/>
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B54" s="2"/>
       <c r="C54" t="s" s="2">
         <v>30</v>
       </c>
       <c r="D54" t="s" s="2">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="E54" s="2"/>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B55" s="2"/>
       <c r="C55" t="s" s="2">
         <v>30</v>
       </c>
       <c r="D55" t="s" s="2">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="E55" s="2"/>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B56" s="2"/>
       <c r="C56" t="s" s="2">
         <v>30</v>
       </c>
       <c r="D56" t="s" s="2">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="E56" s="2"/>
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B57" s="2"/>
       <c r="C57" t="s" s="2">
         <v>30</v>
       </c>
       <c r="D57" t="s" s="2">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="E57" s="2"/>
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B58" s="2"/>
       <c r="C58" t="s" s="2">
         <v>30</v>
       </c>
       <c r="D58" t="s" s="2">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="E58" s="2"/>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B59" s="2"/>
       <c r="C59" t="s" s="2">
         <v>30</v>
       </c>
       <c r="D59" t="s" s="2">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="E59" s="2"/>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B60" s="2"/>
       <c r="C60" t="s" s="2">
         <v>30</v>
       </c>
       <c r="D60" t="s" s="2">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="E60" s="2"/>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B61" s="2"/>
       <c r="C61" t="s" s="2">
         <v>30</v>
       </c>
       <c r="D61" t="s" s="2">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="E61" s="2"/>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B62" s="2"/>
       <c r="C62" t="s" s="2">
         <v>30</v>
       </c>
       <c r="D62" t="s" s="2">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="E62" s="2"/>
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B63" s="2"/>
       <c r="C63" t="s" s="2">
         <v>30</v>
       </c>
       <c r="D63" t="s" s="2">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="E63" s="2"/>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B64" s="2"/>
       <c r="C64" t="s" s="2">
         <v>30</v>
       </c>
       <c r="D64" t="s" s="2">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="E64" s="2"/>
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B65" s="2"/>
       <c r="C65" t="s" s="2">
         <v>30</v>
       </c>
       <c r="D65" t="s" s="2">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="E65" s="2"/>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B66" s="2"/>
       <c r="C66" t="s" s="2">
         <v>30</v>
       </c>
       <c r="D66" t="s" s="2">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="E66" s="2"/>
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B67" s="2"/>
       <c r="C67" t="s" s="2">
         <v>30</v>
       </c>
       <c r="D67" t="s" s="2">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="E67" s="2"/>
     </row>
